--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260617.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260617.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2,050,330</t>
+          <t>65,390,741</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>65,390,741</t>
+          <t>2,050,330</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,210,492</t>
+          <t>105,255,916</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>105,255,916</t>
+          <t>1,210,492</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>198,865,819</t>
+          <t>231,955,093</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>231,955,093</t>
+          <t>198,865,819</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>23,224,815</t>
+          <t>238,931,925</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>238,931,925</t>
+          <t>23,224,815</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202607NYF</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>台灣50ETF股票期貨</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,738</t>
+          <t>20,550,083</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>202607NYF</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>台灣50ETF股票期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>20,550,083</t>
+          <t>1,738</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
